--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00219_18600707.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.1.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -963,7 +963,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00219_18600707.1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y91"/>
+  <dimension ref="A1:Y53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+671B CJK UNIFIED IDEOGRAPH-671B | isolated marker/symbol line :: 望</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 8</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: isolated marker/symbol line :: 9</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]V</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -669,14 +673,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>814</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>L568: candidate OCR token mismatch vs other OCR: "free" vs "fire" :: One Year. Third Â· A free Season Admission</t>
+          <t>L568: candidate OCR token mismatch vs other OCR: "free" vs "fire" :: One Year. Third · A free Season Admission</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr"/>
@@ -692,24 +696,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: -â‚¬And Commercial Advertiser,</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 0</t>
+          <t>L34: stray/suspicious non-ASCII glyph(s): U+671B CJK UNIFIED IDEOGRAPH-671B | isolated marker/symbol line :: 望</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 7</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •.</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -729,7 +733,7 @@
       <c r="V3" s="1" t="inlineStr"/>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
+          <t>L1126: abbreviation/spacing may be garbled :: N.B.As the Messrs. Panner’s engage-</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -771,24 +775,24 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
+          <t>L143: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FREDERICK STOBBS. â€” /_____</t>
+          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: -€And Commercial Advertiser,</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: r</t>
+          <t>L36: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: n</t>
+          <t>L5: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -818,12 +822,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -846,24 +850,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: head â€”</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ountryâ€”a record, the like of which</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: ç­‰</t>
+          <t>L40: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L117: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -921,30 +925,30 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L199: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Then, with a curling lip â€”</t>
+          <t>L262: stray/suspicious non-ASCII glyph(s): U+8449 CJK UNIFIED IDEOGRAPH-8449 | isolated marker/symbol line :: 葉</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: e digestive organÃ© are restored to their</t>
+          <t>L208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ending 31st December, on such of •• said</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: -</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+7B49 CJK UNIFIED IDEOGRAPH-7B49 | isolated marker/symbol line :: 等</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 0</t>
+          <t>L144: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
+          <t>L804: punctuation artifact: repeated periods :: bin’s, Pinet, Castillon’s, &amp;e..</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -996,24 +1000,24 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: that I might take it back; adding â€”" I</t>
+          <t>L366: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一 1.</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: :the patientâ€™s sy stem,</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L132: isolated marker/symbol line :: D</t>
+          <t>L77: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: Â«</t>
+          <t>L146: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -1071,24 +1075,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L366: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€ 1.</t>
+          <t>L725: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: wayâ€™s Pills are the best remedy</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L143: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L132: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 1</t>
+          <t>L153: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1146,24 +1150,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L376: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œAnd the wind, Lady Alice, was</t>
+          <t>L767: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: PORTERS—Bridge's, Hibbe, Hibbert's ， and Guin-</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: pass the housekeeperâ€™s door, and she</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: o</t>
+          <t>L143: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: C</t>
+          <t>L157: isolated marker/symbol line :: «</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1171,7 +1175,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
+          <t>L381: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1189,12 +1193,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1217,24 +1221,24 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Drsrnrata â€” No porooe with thie distres-</t>
+          <t>L828: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sleeps but lightly.â€™</t>
+          <t>L507: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: commends i self as the only relinb • prepara-</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
+          <t>L149: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L277: isolated marker/symbol line :: 9</t>
+          <t>L169: isolated marker/symbol line :: ‘s</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1242,7 +1246,7 @@
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •There la considerable saving by taking</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1265,7 +1269,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1288,24 +1292,24 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases.â€” Never falls to era-</t>
+          <t>L843: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: ALSO} 一</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are we near the housekeeperâ€™s</t>
+          <t>L703: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: system subject to ■ return of the disease—</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L207: isolated marker/symbol line :: 9</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L170: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+          <t>L421: line starts with punctuation glued to text :: ** And the wind. Lady Alice, was, meet all the ghosts in or out of Hades,</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1331,12 +1335,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1355,24 +1359,24 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L655: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€Š</t>
+          <t>L995: stray/suspicious non-ASCII glyph(s): U+8449 CJK UNIFIED IDEOGRAPH-8449 | isolated marker/symbol line :: 葉</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L132: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: They would sayâ€”-It is only Lady</t>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L214: isolated marker/symbol line :: a</t>
+          <t>L207: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "" vs "I M0 C Turcotte Cresse" :: I</t>
+          <t>L275: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1380,7 +1384,7 @@
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+          <t>L739: line starts with punctuation glued to text :: -_choice Paintings, Sculp- tended eyes, as if they were the gates</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1422,30 +1426,34 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L659: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
+          <t>L1016: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一 1.</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Alice.â€™ Yet I cannot tell how I shrink</t>
+          <t>L939: stray/suspicious non-ASCII glyph(s): U+25A0 BLACK SQUARE :: ■ January, 1860, at which time the books will</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L262: isolated marker/symbol line :: è‘‰</t>
+          <t>L214: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: C</t>
+          <t>L277: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
       <c r="R13" s="1" t="inlineStr"/>
-      <c r="S13" s="1" t="inlineStr"/>
+      <c r="S13" s="1" t="inlineStr">
+        <is>
+          <t>L753: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
+        </is>
+      </c>
       <c r="T13" s="1" t="inlineStr"/>
       <c r="U13" s="1" t="inlineStr"/>
       <c r="V13" s="1" t="inlineStr"/>
@@ -1466,7 +1474,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1483,32 +1491,32 @@
           <t>L322: suspicious token(s): BowelCom (odd internal casing) :: dary BowelCom</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Medienes wne carrd of PillÃ©e of 35 years</t>
-        </is>
-      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from being seen by them. Noâ€”I will</t>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L266: isolated marker/symbol line :: B</t>
+          <t>L262: stray/suspicious non-ASCII glyph(s): U+8449 CJK UNIFIED IDEOGRAPH-8449 | isolated marker/symbol line :: 葉</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line :: 00</t>
+          <t>L364: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
       <c r="R14" s="1" t="inlineStr"/>
-      <c r="S14" s="1" t="inlineStr"/>
+      <c r="S14" s="1" t="inlineStr">
+        <is>
+          <t>L1053: line starts with digit/letter garbage token | suspicious token(s): 1Office (letter/digit mix) :: 1Office Department, recently eloped</t>
+        </is>
+      </c>
       <c r="T14" s="1" t="inlineStr"/>
       <c r="U14" s="1" t="inlineStr"/>
       <c r="V14" s="1" t="inlineStr"/>
@@ -1546,32 +1554,28 @@
           <t>L330: suspicious token(s): FemalaComplaints (odd internal casing) :: FemalaComplaints</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L718: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BRANDIESâ€”Martell's, Henn, Hennessey's, Ro</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L408: isolated marker/symbol line :: A</t>
+          <t>L266: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L840: isolated marker/symbol line :: *</t>
+          <t>L398: isolated marker/symbol line | localized OCR phrase divergence vs other OCR: "" vs "I M0 C Turcotte Cresse" :: I</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L1080: line starts with digit/letter garbage token | suspicious token(s): 1sun (letter/digit mix) :: 1sun who will give information which will</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1609,26 +1613,18 @@
           <t>L346: line starts with lowercase prefix glued to capitalized word | suspicious token(s): rCom (odd internal casing) :: rCom- Venereal</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜s</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L478: isolated marker/symbol line :: 0</t>
+          <t>L408: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L1031: isolated marker/symbol line :: ^1</t>
+          <t>L402: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1672,26 +1668,18 @@
           <t>L370: suspicious token(s): andLondon (odd internal casing) :: words Holloway New York andLondon,"</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L767: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PORTERSâ€”Bridge's, Hibbe, Hibbert's ï¼Œ and Guin-</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L181: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PACAUDâ€™S NEW Bl</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L524: isolated marker/symbol line :: 78</t>
+          <t>L478: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L1092: isolated marker/symbol line :: M</t>
+          <t>L724: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1723,26 +1711,18 @@
           <t>L400: suspicious token(s): M0 (letter/digit mix) :: M0</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ALSO} ä¸€</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ending 31st December, on such of â€¢â€¢ said</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L658: isolated marker/symbol line :: 225</t>
+          <t>L524: isolated marker/symbol line :: 78</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L1100: isolated marker/symbol line :: a</t>
+          <t>L840: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1774,26 +1754,18 @@
           <t>L468: suspicious token(s): AMENT5 (letter/digit mix) :: AMENT5</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€ 1.</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N. Dâ€”The Certificates of the Shares in the</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L671: isolated marker/symbol line :: 350</t>
+          <t>L655: isolated marker/symbol line :: 《</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L1102: isolated marker/symbol line :: 99</t>
+          <t>L1031: isolated marker/symbol line :: ^1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1825,26 +1797,18 @@
           <t>L525: suspicious token(s): 1y (letter/digit mix) :: compa 1y each bottle Prepared by</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Drsrnrata â€” No porooe with thie distres-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€” pany of Canada,â€� as decided at a General</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L672: isolated marker/symbol line :: "</t>
+          <t>L658: isolated marker/symbol line :: 225</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L1107: isolated marker/symbol line :: 8</t>
+          <t>L1092: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1873,29 +1837,21 @@
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
-        </is>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases.â€” Never falls to era-</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: - "How did I come here?â€� headâ€”</t>
-        </is>
-      </c>
+          <t>L735: suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not „</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L673: isolated marker/symbol line :: d</t>
+          <t>L659: isolated marker/symbol line :: “</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L1116: isolated marker/symbol line :: a</t>
+          <t>L1100: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1927,26 +1883,18 @@
           <t>L772: suspicious token(s): LiverComplaint (odd internal casing) :: suffering from Consumption, LiverComplaint, tures. Outlines,</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L1059: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Medienes wne carrd of PillÃ©e of 35 years</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: -â€œ I carried you.â€� â€œ Ah, yes! I am right at last; this</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L682: isolated marker/symbol line :: 75</t>
+          <t>L671: isolated marker/symbol line :: 350</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1102: isolated marker/symbol line :: 99</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1979,21 +1927,17 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L281: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ST. NORBERT Dâ€™ARTHABASKA,</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L684: isolated marker/symbol line :: C</t>
+          <t>L672: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L1107: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -2026,21 +1970,17 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L298: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Then, with a curling lipâ€” is the haunted room: I know my way</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L693: isolated marker/symbol line :: 200</t>
+          <t>L673: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L1146: isolated marker/symbol line :: -</t>
+          <t>L1116: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2073,21 +2013,17 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " Where did you find me, pray ?" now.â€�</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L716: isolated marker/symbol line :: 30</t>
+          <t>L682: isolated marker/symbol line :: 75</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L1148: isolated marker/symbol line :: 1</t>
+          <t>L1136: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2120,21 +2056,17 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L307: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: to go to it.â€� Ity and mustiness, I could not tell. Lit-</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L717: isolated marker/symbol line :: .</t>
+          <t>L684: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L1152: isolated marker/symbol line :: &amp;</t>
+          <t>L1138: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2167,21 +2099,17 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Tis impossible. I see. Your the did I think then what memoriesâ€”</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L724: isolated marker/symbol line :: 27</t>
+          <t>L693: isolated marker/symbol line :: 200</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L1154: isolated marker/symbol line :: #</t>
+          <t>L1146: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2214,21 +2142,17 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L314: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: reviving, she went on through berâ€”would ere long find their being and</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L716: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1148: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2261,21 +2185,17 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L791: isolated marker/symbol line :: 000</t>
+          <t>L717: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L1158: isolated marker/symbol line :: 1</t>
+          <t>L1152: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2308,19 +2228,19 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CAUTION â€”None are genome unless</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L856: isolated marker/symbol line :: T</t>
-        </is>
-      </c>
-      <c r="O30" s="1" t="inlineStr"/>
+          <t>L724: isolated marker/symbol line :: 27</t>
+        </is>
+      </c>
+      <c r="O30" s="1" t="inlineStr">
+        <is>
+          <t>L1154: isolated marker/symbol line :: #</t>
+        </is>
+      </c>
       <c r="P30" s="1" t="inlineStr"/>
       <c r="Q30" s="1" t="inlineStr"/>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2351,19 +2271,19 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L381: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L868: isolated marker/symbol line :: b</t>
-        </is>
-      </c>
-      <c r="O31" s="1" t="inlineStr"/>
+          <t>L725: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O31" s="1" t="inlineStr">
+        <is>
+          <t>L1156: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr"/>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2390,19 +2310,19 @@
       </c>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L388: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢There la considerable saving by taking</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L871: isolated marker/symbol line :: X</t>
-        </is>
-      </c>
-      <c r="O32" s="1" t="inlineStr"/>
+          <t>L791: isolated marker/symbol line :: 000</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L1158: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr"/>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2429,16 +2349,12 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L406: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Why did you not leave me where to forsake it never, never moreâ€”the</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L877: isolated marker/symbol line :: 8</t>
+          <t>L828: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2468,16 +2384,12 @@
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: terrible moon might have distorted that I might take it back; addingâ€”"I</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L904: isolated marker/symbol line :: 103</t>
+          <t>L856: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2507,16 +2419,12 @@
       </c>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L485: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: DR. EATONâ€™S</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L914: isolated marker/symbol line :: 55</t>
+          <t>L868: isolated marker/symbol line :: b</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2546,16 +2454,12 @@
       </c>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: commends i self as the only relinb â€¢ prepara-</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L960: isolated marker/symbol line :: D</t>
+          <t>L871: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2585,16 +2489,12 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L513: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: relieving pain, it has no equalâ€”being an anti</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L995: isolated marker/symbol line :: è‘‰</t>
+          <t>L877: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2624,16 +2524,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: take n ne but Dr. Estonâ€™s INFANTI E COR-</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L1086: isolated marker/symbol line :: 103</t>
+          <t>L904: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2663,14 +2559,14 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L541: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Streets.â€”Near the Post Office.</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>L914: isolated marker/symbol line :: 55</t>
+        </is>
+      </c>
       <c r="O39" s="1" t="inlineStr"/>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
@@ -2698,14 +2594,14 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: did. And I hear it nowâ€”I hear it markable cure ofa case</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
+      <c r="N40" s="1" t="inlineStr">
+        <is>
+          <t>L960: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
       <c r="O40" s="1" t="inlineStr"/>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
@@ -2733,14 +2629,14 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
+      <c r="N41" s="1" t="inlineStr">
+        <is>
+          <t>L995: stray/suspicious non-ASCII glyph(s): U+8449 CJK UNIFIED IDEOGRAPH-8449 | isolated marker/symbol line :: 葉</t>
+        </is>
+      </c>
       <c r="O41" s="1" t="inlineStr"/>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
@@ -2768,14 +2664,14 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L636: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: FENDTâ€™S</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
+      <c r="N42" s="1" t="inlineStr">
+        <is>
+          <t>L1086: isolated marker/symbol line :: 103</t>
+        </is>
+      </c>
       <c r="O42" s="1" t="inlineStr"/>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
@@ -2803,11 +2699,7 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LADIESâ€™ UNDERCLOTHING,</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr"/>
@@ -2838,11 +2730,7 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L669: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™ MORNING &amp; BREAKFAST</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr"/>
@@ -2873,11 +2761,7 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 211 and 23 Notre Dame â€” al</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr"/>
@@ -2908,11 +2792,7 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L690: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints â€”In the south and west, where</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr"/>
@@ -2943,11 +2823,7 @@
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L696: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DYSPEPSIA â€”No person with this distres-</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr"/>
@@ -2978,11 +2854,7 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to â– return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr"/>
@@ -3013,11 +2885,7 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines to permanent. â€”</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr"/>
@@ -3048,11 +2916,7 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L709: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lockjaw.â€”The following very re-</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr"/>
@@ -3083,11 +2947,7 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The angry glow faded from her face, dicaleâ€”A poor woman at Verneuil</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr"/>
@@ -3118,11 +2978,7 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: One Year. Third - A fire. Season Admission her, and rising from the couch. â€œI do!</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr"/>
@@ -3153,11 +3009,7 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 54a (letter/digit mix) :: to the Galleries. 54a, Broadway, New York not â€ž</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr"/>
@@ -3173,1184 +3025,6 @@
       <c r="X53" s="1" t="inlineStr"/>
       <c r="Y53" s="1" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L742: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: and Foreign Artists. | â€œ I do not hear it,â€� she said, after a</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
-      <c r="R54" s="1" t="inlineStr"/>
-      <c r="S54" s="1" t="inlineStr"/>
-      <c r="T54" s="1" t="inlineStr"/>
-      <c r="U54" s="1" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
-      <c r="W54" s="1" t="inlineStr"/>
-      <c r="X54" s="1" t="inlineStr"/>
-      <c r="Y54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr"/>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L744: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: The beautiful Engraving, Which every Sub- â€žit must be now.â€� Then</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="inlineStr"/>
-      <c r="S55" s="1" t="inlineStr"/>
-      <c r="T55" s="1" t="inlineStr"/>
-      <c r="U55" s="1" t="inlineStr"/>
-      <c r="V55" s="1" t="inlineStr"/>
-      <c r="W55" s="1" t="inlineStr"/>
-      <c r="X55" s="1" t="inlineStr"/>
-      <c r="Y55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr"/>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 4. Shakspeare and his Friends,â€� turning towards me. she laid her hand</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
-      <c r="R56" s="1" t="inlineStr"/>
-      <c r="S56" s="1" t="inlineStr"/>
-      <c r="T56" s="1" t="inlineStr"/>
-      <c r="U56" s="1" t="inlineStr"/>
-      <c r="V56" s="1" t="inlineStr"/>
-      <c r="W56" s="1" t="inlineStr"/>
-      <c r="X56" s="1" t="inlineStr"/>
-      <c r="Y56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr"/>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L753: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ either the walls of the parlor, library, or of mine, so wide open that I could see the</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="inlineStr"/>
-      <c r="S57" s="1" t="inlineStr"/>
-      <c r="T57" s="1" t="inlineStr"/>
-      <c r="U57" s="1" t="inlineStr"/>
-      <c r="V57" s="1" t="inlineStr"/>
-      <c r="W57" s="1" t="inlineStr"/>
-      <c r="X57" s="1" t="inlineStr"/>
-      <c r="Y57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L785: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: J HOWARD MARCH &amp; CO.â€™s MADEI-</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
-      <c r="R58" s="1" t="inlineStr"/>
-      <c r="S58" s="1" t="inlineStr"/>
-      <c r="T58" s="1" t="inlineStr"/>
-      <c r="U58" s="1" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
-      <c r="W58" s="1" t="inlineStr"/>
-      <c r="X58" s="1" t="inlineStr"/>
-      <c r="Y58" s="1" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L789: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: JUL S ROBIN &amp; CO.â€™S COGNAC BRAN-</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
-      <c r="R59" s="1" t="inlineStr"/>
-      <c r="S59" s="1" t="inlineStr"/>
-      <c r="T59" s="1" t="inlineStr"/>
-      <c r="U59" s="1" t="inlineStr"/>
-      <c r="V59" s="1" t="inlineStr"/>
-      <c r="W59" s="1" t="inlineStr"/>
-      <c r="X59" s="1" t="inlineStr"/>
-      <c r="Y59" s="1" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr"/>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L792: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OFFLEY. CE AMP &amp; co.â€™s PORT WIN S</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="inlineStr"/>
-      <c r="S60" s="1" t="inlineStr"/>
-      <c r="T60" s="1" t="inlineStr"/>
-      <c r="U60" s="1" t="inlineStr"/>
-      <c r="V60" s="1" t="inlineStr"/>
-      <c r="W60" s="1" t="inlineStr"/>
-      <c r="X60" s="1" t="inlineStr"/>
-      <c r="Y60" s="1" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr"/>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L794: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: WM YOUNGER &amp; CO.â€™S EDINBURGH</t>
-        </is>
-      </c>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="inlineStr"/>
-      <c r="S61" s="1" t="inlineStr"/>
-      <c r="T61" s="1" t="inlineStr"/>
-      <c r="U61" s="1" t="inlineStr"/>
-      <c r="V61" s="1" t="inlineStr"/>
-      <c r="W61" s="1" t="inlineStr"/>
-      <c r="X61" s="1" t="inlineStr"/>
-      <c r="Y61" s="1" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr"/>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" s="1" t="inlineStr"/>
-      <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L802: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: for sale on very advantageous terms:â€”</t>
-        </is>
-      </c>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr"/>
-      <c r="R62" s="1" t="inlineStr"/>
-      <c r="S62" s="1" t="inlineStr"/>
-      <c r="T62" s="1" t="inlineStr"/>
-      <c r="U62" s="1" t="inlineStr"/>
-      <c r="V62" s="1" t="inlineStr"/>
-      <c r="W62" s="1" t="inlineStr"/>
-      <c r="X62" s="1" t="inlineStr"/>
-      <c r="Y62" s="1" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr"/>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: BRANDIES-Martellâ€™s, Hennesseyâ€™s, Ro-</t>
-        </is>
-      </c>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr"/>
-      <c r="R63" s="1" t="inlineStr"/>
-      <c r="S63" s="1" t="inlineStr"/>
-      <c r="T63" s="1" t="inlineStr"/>
-      <c r="U63" s="1" t="inlineStr"/>
-      <c r="V63" s="1" t="inlineStr"/>
-      <c r="W63" s="1" t="inlineStr"/>
-      <c r="X63" s="1" t="inlineStr"/>
-      <c r="Y63" s="1" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: binâ€™s, Pinet, Castillonâ€™s, &amp;e..</t>
-        </is>
-      </c>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr"/>
-      <c r="R64" s="1" t="inlineStr"/>
-      <c r="S64" s="1" t="inlineStr"/>
-      <c r="T64" s="1" t="inlineStr"/>
-      <c r="U64" s="1" t="inlineStr"/>
-      <c r="V64" s="1" t="inlineStr"/>
-      <c r="W64" s="1" t="inlineStr"/>
-      <c r="X64" s="1" t="inlineStr"/>
-      <c r="Y64" s="1" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr"/>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L806: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GINSâ€”Holland and English, of best brands</t>
-        </is>
-      </c>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr"/>
-      <c r="R65" s="1" t="inlineStr"/>
-      <c r="S65" s="1" t="inlineStr"/>
-      <c r="T65" s="1" t="inlineStr"/>
-      <c r="U65" s="1" t="inlineStr"/>
-      <c r="V65" s="1" t="inlineStr"/>
-      <c r="W65" s="1" t="inlineStr"/>
-      <c r="X65" s="1" t="inlineStr"/>
-      <c r="Y65" s="1" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr"/>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ALES Bassâ€™, Allsoppâ€™s and Youngerâ€™s, in</t>
-        </is>
-      </c>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr"/>
-      <c r="R66" s="1" t="inlineStr"/>
-      <c r="S66" s="1" t="inlineStr"/>
-      <c r="T66" s="1" t="inlineStr"/>
-      <c r="U66" s="1" t="inlineStr"/>
-      <c r="V66" s="1" t="inlineStr"/>
-      <c r="W66" s="1" t="inlineStr"/>
-      <c r="X66" s="1" t="inlineStr"/>
-      <c r="Y66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr"/>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L815: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: PORTERSâ€”Bridgeâ€™s, Hibbertâ€™s, and Guin-</t>
-        </is>
-      </c>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr"/>
-      <c r="R67" s="1" t="inlineStr"/>
-      <c r="S67" s="1" t="inlineStr"/>
-      <c r="T67" s="1" t="inlineStr"/>
-      <c r="U67" s="1" t="inlineStr"/>
-      <c r="V67" s="1" t="inlineStr"/>
-      <c r="W67" s="1" t="inlineStr"/>
-      <c r="X67" s="1" t="inlineStr"/>
-      <c r="Y67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr"/>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L816: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: nessâ€™, in wood and bottle</t>
-        </is>
-      </c>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr"/>
-      <c r="R68" s="1" t="inlineStr"/>
-      <c r="S68" s="1" t="inlineStr"/>
-      <c r="T68" s="1" t="inlineStr"/>
-      <c r="U68" s="1" t="inlineStr"/>
-      <c r="V68" s="1" t="inlineStr"/>
-      <c r="W68" s="1" t="inlineStr"/>
-      <c r="X68" s="1" t="inlineStr"/>
-      <c r="Y68" s="1" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr"/>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L818: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WHISKIESâ€”SCOTCH and IRISH, of the</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr"/>
-      <c r="R69" s="1" t="inlineStr"/>
-      <c r="S69" s="1" t="inlineStr"/>
-      <c r="T69" s="1" t="inlineStr"/>
-      <c r="U69" s="1" t="inlineStr"/>
-      <c r="V69" s="1" t="inlineStr"/>
-      <c r="W69" s="1" t="inlineStr"/>
-      <c r="X69" s="1" t="inlineStr"/>
-      <c r="Y69" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr"/>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L822: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: PORT WINESâ€”Offley &amp; Co â€˜s. Spademan a</t>
-        </is>
-      </c>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr"/>
-      <c r="R70" s="1" t="inlineStr"/>
-      <c r="S70" s="1" t="inlineStr"/>
-      <c r="T70" s="1" t="inlineStr"/>
-      <c r="U70" s="1" t="inlineStr"/>
-      <c r="V70" s="1" t="inlineStr"/>
-      <c r="W70" s="1" t="inlineStr"/>
-      <c r="X70" s="1" t="inlineStr"/>
-      <c r="Y70" s="1" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr"/>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L825: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: SHERRIESâ€” Crump. Suter &amp; Co.â€™s, Do</t>
-        </is>
-      </c>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr"/>
-      <c r="R71" s="1" t="inlineStr"/>
-      <c r="S71" s="1" t="inlineStr"/>
-      <c r="T71" s="1" t="inlineStr"/>
-      <c r="U71" s="1" t="inlineStr"/>
-      <c r="V71" s="1" t="inlineStr"/>
-      <c r="W71" s="1" t="inlineStr"/>
-      <c r="X71" s="1" t="inlineStr"/>
-      <c r="Y71" s="1" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr"/>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN :: meeq.â€˜s, Pemartinâ€™s &amp;c.</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr"/>
-      <c r="R72" s="1" t="inlineStr"/>
-      <c r="S72" s="1" t="inlineStr"/>
-      <c r="T72" s="1" t="inlineStr"/>
-      <c r="U72" s="1" t="inlineStr"/>
-      <c r="V72" s="1" t="inlineStr"/>
-      <c r="W72" s="1" t="inlineStr"/>
-      <c r="X72" s="1" t="inlineStr"/>
-      <c r="Y72" s="1" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr"/>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr"/>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CHAMPAGNESâ€”Meet &amp; Chandonâ€™s, and</t>
-        </is>
-      </c>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr"/>
-      <c r="R73" s="1" t="inlineStr"/>
-      <c r="S73" s="1" t="inlineStr"/>
-      <c r="T73" s="1" t="inlineStr"/>
-      <c r="U73" s="1" t="inlineStr"/>
-      <c r="V73" s="1" t="inlineStr"/>
-      <c r="W73" s="1" t="inlineStr"/>
-      <c r="X73" s="1" t="inlineStr"/>
-      <c r="Y73" s="1" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L831: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CLARETSâ€”Of various ages, in wood and</t>
-        </is>
-      </c>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr"/>
-      <c r="R74" s="1" t="inlineStr"/>
-      <c r="S74" s="1" t="inlineStr"/>
-      <c r="T74" s="1" t="inlineStr"/>
-      <c r="U74" s="1" t="inlineStr"/>
-      <c r="V74" s="1" t="inlineStr"/>
-      <c r="W74" s="1" t="inlineStr"/>
-      <c r="X74" s="1" t="inlineStr"/>
-      <c r="Y74" s="1" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™d Arichat,</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr"/>
-      <c r="R75" s="1" t="inlineStr"/>
-      <c r="S75" s="1" t="inlineStr"/>
-      <c r="T75" s="1" t="inlineStr"/>
-      <c r="U75" s="1" t="inlineStr"/>
-      <c r="V75" s="1" t="inlineStr"/>
-      <c r="W75" s="1" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr"/>
-      <c r="Y75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr"/>
-      <c r="R76" s="1" t="inlineStr"/>
-      <c r="S76" s="1" t="inlineStr"/>
-      <c r="T76" s="1" t="inlineStr"/>
-      <c r="U76" s="1" t="inlineStr"/>
-      <c r="V76" s="1" t="inlineStr"/>
-      <c r="W76" s="1" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr"/>
-      <c r="Y76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L883: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: I'll ES â€”The original Proprietor of these</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L912: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: youâ€”you could not help it. I will</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L965: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: duties of Customs;â€� the duty, heret fore im-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER, U+02DC SMALL TILDE :: %â€œ Scottsâ€� Brand, Choiâ€˜e.</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1064: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: this night or morningâ€”hichever it</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1065: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI It is past midnight, but not morn-</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1066: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ofthe papers from the Reading Tables of the ing yet,â€� she replied ;" I always know</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1070: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ There is; but we should have to with her riding-master.</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1082: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ALSO,â€”</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CO.â€™</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | abbreviation/spacing may be garbled :: N.B.As the Messrs. Pannerâ€™s engage-</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1136: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
